--- a/docs/Test_Report/Wdg/TestPlanExecutionReport_Wdg.xlsx
+++ b/docs/Test_Report/Wdg/TestPlanExecutionReport_Wdg.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Test Strategy Compliance'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Test Plan | Execution Report'!$A$1:$U$68</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -43,7 +43,7 @@
       <sz val="16"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -77,11 +77,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="000000FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
@@ -104,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -136,13 +131,10 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -724,7 +716,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759,MCAL-30818</t>
+          <t>MCAL-32337,MCAL-32340</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -734,7 +726,7 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09 07:16:23.868231-05:00 CDT</t>
+          <t>2025-08-29 04:12:20.065549-05:00 CDT</t>
         </is>
       </c>
     </row>
@@ -806,12 +798,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>61</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -843,7 +835,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -868,7 +860,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -880,12 +872,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1028,12 +1020,12 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>67</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
@@ -1053,7 +1045,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
     </row>
@@ -1119,12 +1111,12 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
@@ -1151,12 +1143,12 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -1183,12 +1175,12 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>100%</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>0%</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1362,7 +1354,7 @@
         </is>
       </c>
       <c r="E2" s="3" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3">
@@ -1372,7 +1364,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="3" t="n"/>
       <c r="D3" s="7" t="inlineStr">
@@ -1381,7 +1373,7 @@
         </is>
       </c>
       <c r="E3" s="7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4">
@@ -1391,7 +1383,7 @@
         </is>
       </c>
       <c r="B4" s="7" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" s="3" t="n"/>
       <c r="D4" s="3" t="n"/>
@@ -1409,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U69"/>
+  <dimension ref="A1:U68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1545,12 +1537,12 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1657,12 +1649,12 @@
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R2" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S2" s="3" t="inlineStr"/>
@@ -1676,12 +1668,12 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1788,12 +1780,12 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S3" s="3" t="inlineStr"/>
@@ -1807,12 +1799,12 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1919,12 +1911,12 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr"/>
@@ -1938,12 +1930,12 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -2050,12 +2042,12 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr"/>
@@ -2069,12 +2061,12 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -2181,12 +2173,12 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr"/>
@@ -2200,12 +2192,12 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -2312,12 +2304,12 @@
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr"/>
@@ -2331,12 +2323,12 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -2443,12 +2435,12 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr"/>
@@ -2462,12 +2454,12 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -2574,12 +2566,12 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr"/>
@@ -2593,12 +2585,12 @@
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
@@ -2705,12 +2697,12 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr"/>
@@ -2724,12 +2716,12 @@
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -2836,12 +2828,12 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr"/>
@@ -2855,12 +2847,12 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
@@ -2967,12 +2959,12 @@
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr"/>
@@ -2986,12 +2978,12 @@
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -3098,12 +3090,12 @@
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr"/>
@@ -3117,12 +3109,12 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
@@ -3229,12 +3221,12 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr"/>
@@ -3248,12 +3240,12 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -3360,12 +3352,12 @@
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr"/>
@@ -3379,12 +3371,12 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
@@ -3491,12 +3483,12 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr"/>
@@ -3510,12 +3502,12 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -3622,12 +3614,12 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr"/>
@@ -3641,12 +3633,12 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
@@ -3753,12 +3745,12 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr"/>
@@ -3772,12 +3764,12 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -3884,12 +3876,12 @@
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr"/>
@@ -3903,12 +3895,12 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
@@ -4015,12 +4007,12 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr"/>
@@ -4034,12 +4026,12 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -4146,12 +4138,12 @@
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr"/>
@@ -4165,12 +4157,12 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -4277,12 +4269,12 @@
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr"/>
@@ -4296,12 +4288,12 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -4408,12 +4400,12 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr"/>
@@ -4427,12 +4419,12 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -4452,7 +4444,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28561,MCAL-28559,MCAL-28560,MCAL-25244</t>
+          <t>MCAL-28561,MCAL-28559,MCAL-25244,MCAL-28560</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -4539,12 +4531,12 @@
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr"/>
@@ -4558,12 +4550,12 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -4583,7 +4575,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25267,MCAL-25243,MCAL-25239,MCAL-25242,MCAL-25240,MCAL-25238,MCAL-25266</t>
+          <t>MCAL-25267,MCAL-25243,MCAL-25239,MCAL-25238,MCAL-25266,MCAL-25240,MCAL-25242</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -4670,12 +4662,12 @@
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr"/>
@@ -4689,12 +4681,12 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
@@ -4801,12 +4793,12 @@
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr"/>
@@ -4820,12 +4812,12 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -4932,12 +4924,12 @@
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr"/>
@@ -4951,12 +4943,12 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -5063,12 +5055,12 @@
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr"/>
@@ -5082,12 +5074,12 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -5194,12 +5186,12 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr"/>
@@ -5213,12 +5205,12 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -5325,12 +5317,12 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr"/>
@@ -5344,12 +5336,12 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -5456,12 +5448,12 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr"/>
@@ -5475,12 +5467,12 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
@@ -5587,12 +5579,12 @@
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr"/>
@@ -5606,12 +5598,12 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -5718,12 +5710,12 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr"/>
@@ -5737,12 +5729,12 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
@@ -5762,7 +5754,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-25255,MCAL-28570,MCAL-28568,MCAL-28567,MCAL-28563,MCAL-28564,MCAL-25295,MCAL-28562,MCAL-28571,MCAL-28569,MCAL-28566,MCAL-28565</t>
+          <t>MCAL-25255,MCAL-28570,MCAL-28568,MCAL-28567,MCAL-28563,MCAL-28564,MCAL-25295,MCAL-28562,MCAL-28571,MCAL-28569,MCAL-28565,MCAL-28566</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -5849,12 +5841,12 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr"/>
@@ -5868,12 +5860,12 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -5980,12 +5972,12 @@
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr"/>
@@ -5999,12 +5991,12 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
@@ -6111,12 +6103,12 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr"/>
@@ -6130,12 +6122,12 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -6242,12 +6234,12 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr"/>
@@ -6261,12 +6253,12 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -6373,12 +6365,12 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr"/>
@@ -6392,12 +6384,12 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -6504,12 +6496,12 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr"/>
@@ -6523,12 +6515,12 @@
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -6635,12 +6627,12 @@
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr"/>
@@ -6654,12 +6646,12 @@
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -6766,12 +6758,12 @@
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr"/>
@@ -6785,12 +6777,12 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -6897,12 +6889,12 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr"/>
@@ -6916,12 +6908,12 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -6941,7 +6933,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-28566,MCAL-28563,MCAL-25254,MCAL-25250,MCAL-28570,MCAL-28562,MCAL-25249,MCAL-28571,MCAL-28569,MCAL-25294,MCAL-25295,MCAL-28568,MCAL-28567,MCAL-28564,MCAL-28565</t>
+          <t>MCAL-28566,MCAL-28563,MCAL-25254,MCAL-25250,MCAL-28570,MCAL-28562,MCAL-25249,MCAL-25294,MCAL-25295,MCAL-28568,MCAL-28567,MCAL-28565,MCAL-28564,MCAL-28571,MCAL-28569</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -7028,12 +7020,12 @@
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr"/>
@@ -7047,12 +7039,12 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
@@ -7159,12 +7151,12 @@
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr"/>
@@ -7178,12 +7170,12 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -7290,12 +7282,12 @@
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr"/>
@@ -7309,12 +7301,12 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30765</t>
+          <t>MCAL-32338</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
@@ -7421,12 +7413,12 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30759</t>
+          <t>MCAL-32337</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Automated Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Automated Tests Run</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr"/>
@@ -7440,12 +7432,12 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -7520,31 +7512,31 @@
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S47" s="3" t="inlineStr"/>
       <c r="T47" s="3" t="inlineStr"/>
-      <c r="U47" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U47" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
@@ -7619,31 +7611,31 @@
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S48" s="3" t="inlineStr"/>
       <c r="T48" s="3" t="inlineStr"/>
-      <c r="U48" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U48" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -7718,31 +7710,31 @@
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S49" s="3" t="inlineStr"/>
       <c r="T49" s="3" t="inlineStr"/>
-      <c r="U49" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U49" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
@@ -7817,31 +7809,31 @@
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S50" s="3" t="inlineStr"/>
       <c r="T50" s="3" t="inlineStr"/>
-      <c r="U50" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U50" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -7916,31 +7908,31 @@
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S51" s="3" t="inlineStr"/>
       <c r="T51" s="3" t="inlineStr"/>
-      <c r="U51" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U51" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -8047,31 +8039,31 @@
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S52" s="3" t="inlineStr"/>
       <c r="T52" s="3" t="inlineStr"/>
-      <c r="U52" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U52" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -8178,31 +8170,31 @@
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S53" s="3" t="inlineStr"/>
       <c r="T53" s="3" t="inlineStr"/>
-      <c r="U53" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U53" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -8277,31 +8269,31 @@
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S54" s="3" t="inlineStr"/>
       <c r="T54" s="3" t="inlineStr"/>
-      <c r="U54" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U54" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -8376,31 +8368,31 @@
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S55" s="3" t="inlineStr"/>
       <c r="T55" s="3" t="inlineStr"/>
-      <c r="U55" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U55" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -8475,31 +8467,31 @@
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S56" s="3" t="inlineStr"/>
       <c r="T56" s="3" t="inlineStr"/>
-      <c r="U56" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U56" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -8574,31 +8566,31 @@
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S57" s="3" t="inlineStr"/>
       <c r="T57" s="3" t="inlineStr"/>
-      <c r="U57" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U57" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -8673,31 +8665,31 @@
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S58" s="3" t="inlineStr"/>
       <c r="T58" s="3" t="inlineStr"/>
-      <c r="U58" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U58" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -8772,31 +8764,31 @@
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S59" s="3" t="inlineStr"/>
       <c r="T59" s="3" t="inlineStr"/>
-      <c r="U59" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U59" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -8871,31 +8863,31 @@
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S60" s="3" t="inlineStr"/>
       <c r="T60" s="3" t="inlineStr"/>
-      <c r="U60" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U60" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -8970,31 +8962,31 @@
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S61" s="3" t="inlineStr"/>
       <c r="T61" s="3" t="inlineStr"/>
-      <c r="U61" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U61" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -9069,31 +9061,31 @@
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S62" s="3" t="inlineStr"/>
       <c r="T62" s="3" t="inlineStr"/>
-      <c r="U62" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U62" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -9200,31 +9192,31 @@
       </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R63" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S63" s="3" t="inlineStr"/>
       <c r="T63" s="3" t="inlineStr"/>
-      <c r="U63" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U63" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
@@ -9331,31 +9323,31 @@
       </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R64" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S64" s="3" t="inlineStr"/>
       <c r="T64" s="3" t="inlineStr"/>
-      <c r="U64" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U64" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -9462,31 +9454,31 @@
       </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R65" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S65" s="3" t="inlineStr"/>
       <c r="T65" s="3" t="inlineStr"/>
-      <c r="U65" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U65" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
@@ -9593,31 +9585,31 @@
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R66" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S66" s="3" t="inlineStr"/>
       <c r="T66" s="3" t="inlineStr"/>
-      <c r="U66" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U66" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -9724,31 +9716,31 @@
       </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R67" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S67" s="3" t="inlineStr"/>
       <c r="T67" s="3" t="inlineStr"/>
-      <c r="U67" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U67" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30819</t>
+          <t>MCAL-32341</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
@@ -9855,123 +9847,24 @@
       </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
-          <t>MCAL-30818</t>
+          <t>MCAL-32340</t>
         </is>
       </c>
       <c r="R68" s="3" t="inlineStr">
         <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
+          <t>F29H85xMCAL_01.03.00: WDG - Manual Tests Run</t>
         </is>
       </c>
       <c r="S68" s="3" t="inlineStr"/>
       <c r="T68" s="3" t="inlineStr"/>
-      <c r="U68" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30819</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-27032</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>Manual Test To Verify AUTOSAR 4.3.1 BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="inlineStr">
-        <is>
-          <t>Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture,Architecture</t>
-        </is>
-      </c>
-      <c r="F69" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-12327,MCAL-12305,MCAL-25467,MCAL-12412,MCAL-12411,MCAL-12410,MCAL-12389,MCAL-12374,MCAL-12355,MCAL-12309,MCAL-12448,MCAL-12395,MCAL-12379,MCAL-12375,MCAL-12446,MCAL-25460,MCAL-25458,MCAL-12345,MCAL-12341,MCAL-12445,MCAL-12356,MCAL-12338,MCAL-12335,MCAL-12333,MCAL-12332,MCAL-12366,MCAL-12306,MCAL-12360,MCAL-12396,MCAL-12427,MCAL-12421,MCAL-12418,MCAL-25456,MCAL-12376,MCAL-12340,MCAL-12316,MCAL-12312,MCAL-12310,MCAL-12361,MCAL-12399,MCAL-12326,MCAL-25455,MCAL-25471,MCAL-25469,MCAL-25461,MCAL-12337,MCAL-12334,MCAL-12323,MCAL-12303,MCAL-12425</t>
-        </is>
-      </c>
-      <c r="G69" s="3" t="inlineStr">
-        <is>
-          <t>F29H85x-evm,F29P58x-evm</t>
-        </is>
-      </c>
-      <c r="H69" s="3" t="inlineStr">
-        <is>
-          <t>Integration</t>
-        </is>
-      </c>
-      <c r="I69" s="3" t="inlineStr">
-        <is>
-          <t>Manually verify all Modules Design requirements are satisfying the AUTOSAR BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="J69" s="3" t="inlineStr">
-        <is>
-          <t>Manual Verification</t>
-        </is>
-      </c>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>Module Design requirements are satisfying the AUTOSAR BSW and SPAL requirements</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>Requirements-Analysis</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="inlineStr">
-        <is>
-          <t>Manual</t>
-        </is>
-      </c>
-      <c r="O69" s="3" t="inlineStr">
-        <is>
-          <t>Full,Sanity</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="inlineStr">
-        <is>
-          <t>Can,Dio,Gpt,Mcu,Port</t>
-        </is>
-      </c>
-      <c r="Q69" s="3" t="inlineStr">
-        <is>
-          <t>MCAL-30818</t>
-        </is>
-      </c>
-      <c r="R69" s="3" t="inlineStr">
-        <is>
-          <t>F29H85xMCAL_01.02.01: WDG - Manual Tests Run</t>
-        </is>
-      </c>
-      <c r="S69" s="3" t="inlineStr"/>
-      <c r="T69" s="3" t="inlineStr"/>
-      <c r="U69" s="11" t="inlineStr">
-        <is>
-          <t>Not Executed</t>
+      <c r="U68" s="10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U69"/>
+  <autoFilter ref="A1:U68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10020,12 +9913,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Test Plan</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Test Plan Key</t>
         </is>
@@ -10047,8 +9940,8 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="n"/>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="A3" s="11" t="n"/>
+      <c r="B3" s="12" t="inlineStr">
         <is>
           <t>Test Plan Name</t>
         </is>
@@ -10070,8 +9963,8 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="n"/>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="A4" s="11" t="n"/>
+      <c r="B4" s="12" t="inlineStr">
         <is>
           <t>Test Case Key</t>
         </is>
@@ -10093,8 +9986,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="n"/>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="A5" s="11" t="n"/>
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Test Case Name</t>
         </is>
@@ -10116,8 +10009,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="n"/>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="A6" s="11" t="n"/>
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Associated Issue(s) Type</t>
         </is>
@@ -10144,8 +10037,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Associated Issue(s) ID(s)</t>
         </is>
@@ -10167,8 +10060,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Test Platform</t>
         </is>
@@ -10190,8 +10083,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Test Level</t>
         </is>
@@ -10207,7 +10100,7 @@
 -- "Not Provided" if no 'Test Scope' is provided in Jira</t>
         </is>
       </c>
-      <c r="D9" s="12" t="inlineStr">
+      <c r="D9" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10219,8 +10112,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="A10" s="11" t="n"/>
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Test Description</t>
         </is>
@@ -10242,8 +10135,8 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="A11" s="11" t="n"/>
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Test Setup</t>
         </is>
@@ -10265,8 +10158,8 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="13" t="inlineStr">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Pass/Fail Criteria</t>
         </is>
@@ -10288,8 +10181,8 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="13" t="inlineStr">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Test Type</t>
         </is>
@@ -10300,7 +10193,7 @@
 (Map Test Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D13" s="12" t="inlineStr">
+      <c r="D13" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10312,15 +10205,15 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="13" t="n"/>
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="12" t="n"/>
       <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Functional:
 Tests covering functional requirements-based  aspects of the software</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10332,8 +10225,8 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="13" t="n"/>
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="12" t="n"/>
       <c r="C15" s="3" t="inlineStr">
         <is>
           <t>Compatability:
@@ -10341,7 +10234,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing that measures the degree to which a test item can function satisfactorily alongside other independent products in a shared environment (co-existence), and where necessary, exchanges information with other systems or components (interoperability)</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
+      <c r="D15" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10353,15 +10246,15 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="13" t="n"/>
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="12" t="n"/>
       <c r="C16" s="3" t="inlineStr">
         <is>
           <t>Usability:
 Test Case covers usability/api/look and feel aspects of the module including out-of box (OOB) experience</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10373,15 +10266,15 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="13" t="n"/>
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="12" t="n"/>
       <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Fault Injection:
 Testing based on injection of errors or faults to ensure no unintended consequences</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
+      <c r="D17" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10393,8 +10286,8 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="13" t="n"/>
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="12" t="n"/>
       <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Performance: 
@@ -10402,7 +10295,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item accomplishes its designated functions within given constraints of time and other resources</t>
         </is>
       </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10414,8 +10307,8 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="13" t="n"/>
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="12" t="n"/>
       <c r="C19" s="3" t="inlineStr">
         <is>
           <t>Reliability: 
@@ -10423,7 +10316,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ability of a test item to perform its required functions, including evaluating the frequency with which failures occur, when it is used under stated conditions for a specified period of time</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D19" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10435,8 +10328,8 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="13" t="n"/>
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="12" t="n"/>
       <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Stress:
@@ -10444,7 +10337,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of performance efficiency testing conducted to evaluate a test item's behaviour under conditions of loading above anticipated or specified capacity requirements, or of resource availability below minimum specified requirements</t>
         </is>
       </c>
-      <c r="D20" s="12" t="inlineStr">
+      <c r="D20" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10456,8 +10349,8 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="13" t="n"/>
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="12" t="n"/>
       <c r="C21" s="3" t="inlineStr">
         <is>
           <t>Security:
@@ -10465,7 +10358,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the degree to which a test item, and associated data and information, are protected so that unauthorized persons or systems cannot use, read, or modify them, and authorized persons or systems are not denied access to them</t>
         </is>
       </c>
-      <c r="D21" s="12" t="inlineStr">
+      <c r="D21" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10477,8 +10370,8 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="13" t="n"/>
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="12" t="n"/>
       <c r="C22" s="3" t="inlineStr">
         <is>
           <t>Maintainability:
@@ -10486,7 +10379,7 @@
 ISO/IEC/IEEE 29119-1 Defn: test type conducted to evaluate the degree of effectiveness and efficiency with which a test item may be modified</t>
         </is>
       </c>
-      <c r="D22" s="12" t="inlineStr">
+      <c r="D22" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10498,8 +10391,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="13" t="n"/>
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="12" t="n"/>
       <c r="C23" s="3" t="inlineStr">
         <is>
           <t>Portability:
@@ -10507,7 +10400,7 @@
 ISO/IEC/IEEE 29119-1 Defn: type of testing conducted to evaluate the ease with which a test item can be transferred from one hardware or software environment to another, including the level of modification needed for it to be executed in various types of environment</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
+      <c r="D23" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10519,8 +10412,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="13" t="inlineStr">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="12" t="inlineStr">
         <is>
           <t>Test Design Technique</t>
         </is>
@@ -10532,7 +10425,7 @@
 (Map Test Derivation Method from Qmetry)</t>
         </is>
       </c>
-      <c r="D24" s="12" t="inlineStr">
+      <c r="D24" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10544,8 +10437,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="13" t="n"/>
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="12" t="n"/>
       <c r="C25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Requirements-Analysis:
@@ -10553,7 +10446,7 @@
 </t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10565,15 +10458,15 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="13" t="n"/>
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="12" t="n"/>
       <c r="C26" s="3" t="inlineStr">
         <is>
           <t>Boundary Value Analysis:
 Test cases that apply to interfaces and values approaching and crossing the boundaries and out of range values</t>
         </is>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D26" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10585,15 +10478,15 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n"/>
-      <c r="B27" s="13" t="n"/>
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="12" t="n"/>
       <c r="C27" s="3" t="inlineStr">
         <is>
           <t>Error Guessing:
 Test cases established based on lessons learned and expert judgement to determine situations that may cause software failures or errors to appear</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
+      <c r="D27" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10605,28 +10498,28 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="13" t="n"/>
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="12" t="n"/>
       <c r="C28" s="3" t="inlineStr">
         <is>
           <t>Other (Use case analysis; Customer Usage; Requirement analysis; Failure Mode analysis):
 Teams are encouraged to use techniques defined by standards such as ISO/IEC/IEEE 29119-4; which needs to be refelcted within Qmetry</t>
         </is>
       </c>
-      <c r="D28" s="12" t="inlineStr">
+      <c r="D28" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E28" s="12" t="inlineStr">
+      <c r="E28" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n"/>
-      <c r="B29" s="13" t="inlineStr">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="12" t="inlineStr">
         <is>
           <t>Test Execution Type</t>
         </is>
@@ -10636,7 +10529,7 @@
           <t>Identifies whether the case is automated or manually or Semi-Automated executed</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
+      <c r="D29" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10648,8 +10541,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="13" t="inlineStr">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="12" t="inlineStr">
         <is>
           <t>Test Category</t>
         </is>
@@ -10659,7 +10552,7 @@
           <t>Test Categories represent sets of tests that are commonly used.</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D30" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10671,15 +10564,15 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="13" t="n"/>
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="12" t="n"/>
       <c r="C31" s="3" t="inlineStr">
         <is>
           <t>Sanity:
 This Test case is identified to run for Sanity Checks. These are mainly the basic tests that need to be run as part of entry to validate phase</t>
         </is>
       </c>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10691,15 +10584,15 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="13" t="n"/>
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="12" t="n"/>
       <c r="C32" s="3" t="inlineStr">
         <is>
           <t>Full:
 This category means running all test cases for identified releases</t>
         </is>
       </c>
-      <c r="D32" s="12" t="inlineStr">
+      <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10711,15 +10604,15 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="13" t="n"/>
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="12" t="n"/>
       <c r="C33" s="3" t="inlineStr">
         <is>
           <t>Base Regression:
 This Test case is identified to run for the Base Regression / maintenance releases</t>
         </is>
       </c>
-      <c r="D33" s="12" t="inlineStr">
+      <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
@@ -10731,8 +10624,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="13" t="inlineStr">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>Test Component(s)</t>
         </is>
@@ -10742,24 +10635,24 @@
           <t xml:space="preserve">The field provides the Component(s) (in Jira) to which the Test Case is mapped to. </t>
         </is>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D34" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E34" s="11" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="13" t="inlineStr">
         <is>
           <t>Test Execution</t>
         </is>
       </c>
-      <c r="B35" s="13" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>Build/Release Key</t>
         </is>
@@ -10781,8 +10674,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="n"/>
-      <c r="B36" s="13" t="inlineStr">
+      <c r="A36" s="13" t="n"/>
+      <c r="B36" s="12" t="inlineStr">
         <is>
           <t>Defect Key</t>
         </is>
@@ -10804,8 +10697,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="n"/>
-      <c r="B37" s="13" t="inlineStr">
+      <c r="A37" s="13" t="n"/>
+      <c r="B37" s="12" t="inlineStr">
         <is>
           <t>Defect Summary</t>
         </is>
@@ -10827,8 +10720,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="n"/>
-      <c r="B38" s="13" t="inlineStr">
+      <c r="A38" s="13" t="n"/>
+      <c r="B38" s="12" t="inlineStr">
         <is>
           <t>Overall Status</t>
         </is>
@@ -10851,8 +10744,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="n"/>
-      <c r="B39" s="13" t="n"/>
+      <c r="A39" s="13" t="n"/>
+      <c r="B39" s="12" t="n"/>
       <c r="C39" s="3" t="inlineStr">
         <is>
           <t>PASS
@@ -10871,8 +10764,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="n"/>
-      <c r="B40" s="13" t="n"/>
+      <c r="A40" s="13" t="n"/>
+      <c r="B40" s="12" t="n"/>
       <c r="C40" s="3" t="inlineStr">
         <is>
           <t>FAIL
@@ -10891,8 +10784,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="n"/>
-      <c r="B41" s="13" t="n"/>
+      <c r="A41" s="13" t="n"/>
+      <c r="B41" s="12" t="n"/>
       <c r="C41" s="3" t="inlineStr">
         <is>
           <t>BLOCKED
@@ -10911,8 +10804,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="n"/>
-      <c r="B42" s="13" t="n"/>
+      <c r="A42" s="13" t="n"/>
+      <c r="B42" s="12" t="n"/>
       <c r="C42" s="3" t="inlineStr">
         <is>
           <t>WIP
